--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3763C909-4495-674E-869A-2F75F3A0B6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43464F0-1132-8347-961F-737873278A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Date</t>
   </si>
@@ -189,7 +189,10 @@
     <t>NO CLASS</t>
   </si>
   <si>
-    <t>01-Intro_to_Course.html</t>
+    <t>/slides/02-Summarizing_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/01-Intro_to_Course.html</t>
   </si>
 </sst>
 </file>
@@ -603,7 +606,7 @@
         <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E2" t="s">
         <v>29</v>
@@ -622,6 +625,9 @@
       </c>
       <c r="C3" t="s">
         <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
       </c>
       <c r="E3" t="s">
         <v>30</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43464F0-1132-8347-961F-737873278A5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2EDBC9-2F46-CB49-B19F-0FA06280FDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -57,9 +57,6 @@
     <t>Slides</t>
   </si>
   <si>
-    <t>Foundation for Inference</t>
-  </si>
-  <si>
     <t>Linear Regression</t>
   </si>
   <si>
@@ -102,9 +99,6 @@
     <t>Intro to the Course / Intro to Data</t>
   </si>
   <si>
-    <t>Probability and Distributions</t>
-  </si>
-  <si>
     <t>Maximum Likelihood Estimation and Logistic Regression</t>
   </si>
   <si>
@@ -193,6 +187,13 @@
   </si>
   <si>
     <t>/slides/01-Intro_to_Course.html</t>
+  </si>
+  <si>
+    <t>NO CLASS - Makeup TBD</t>
+  </si>
+  <si>
+    <t>Probability and Distributions / 
+Foundation for Inference</t>
   </si>
 </sst>
 </file>
@@ -583,16 +584,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D1" t="s">
         <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -600,19 +601,19 @@
         <v>45895</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -621,19 +622,19 @@
         <v>45902</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -642,34 +643,34 @@
         <v>45909</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
+        <v>45916</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <f t="shared" si="0"/>
-        <v>45916</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>33</v>
-      </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -678,7 +679,7 @@
         <v>45923</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -690,13 +691,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -705,7 +706,7 @@
         <v>45937</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -714,13 +715,13 @@
         <v>45944</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -732,13 +733,13 @@
         <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -747,16 +748,16 @@
         <v>45958</v>
       </c>
       <c r="B11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -768,13 +769,13 @@
         <v>5</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -783,10 +784,10 @@
         <v>45972</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="4"/>
     </row>
@@ -796,7 +797,7 @@
         <v>45979</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -806,7 +807,7 @@
         <v>45986</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -816,10 +817,10 @@
         <v>45993</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C16" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -829,7 +830,7 @@
         <v>46000</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2"/>
     </row>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2EDBC9-2F46-CB49-B19F-0FA06280FDD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8B1551-5325-C041-AA8C-C4D9B68304C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Date</t>
   </si>
@@ -189,11 +189,16 @@
     <t>/slides/01-Intro_to_Course.html</t>
   </si>
   <si>
-    <t>NO CLASS - Makeup TBD</t>
-  </si>
-  <si>
-    <t>Probability and Distributions / 
-Foundation for Inference</t>
+    <t>/slides/03-Probability_and_Distributions.html</t>
+  </si>
+  <si>
+    <t>/slides/05-Foundation_for_Inference.html</t>
+  </si>
+  <si>
+    <t>Foundation for Inference</t>
+  </si>
+  <si>
+    <t>Probability and Distributions</t>
   </si>
 </sst>
 </file>
@@ -643,11 +648,14 @@
         <v>45909</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
+      <c r="D4" t="s">
+        <v>51</v>
+      </c>
       <c r="E4" t="s">
         <v>29</v>
       </c>
@@ -655,16 +663,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <f t="shared" si="0"/>
         <v>45916</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>31</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E8B1551-5325-C041-AA8C-C4D9B68304C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B17BEC-A27A-7547-BCE6-BABA2F0FEA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -244,16 +244,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -728,12 +725,6 @@
       <c r="B9" t="s">
         <v>48</v>
       </c>
-      <c r="E9" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -747,10 +738,10 @@
         <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -765,10 +756,10 @@
         <v>14</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -783,10 +774,10 @@
         <v>39</v>
       </c>
       <c r="E12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F12" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -800,7 +791,12 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="4"/>
+      <c r="E13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F13" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" s="1">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7B17BEC-A27A-7547-BCE6-BABA2F0FEA27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5E1B34-815B-F64D-957C-E29F55A82F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Date</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Probability and Distributions</t>
+  </si>
+  <si>
+    <t>/slides/06-Inference_for_Categorical_Data.html</t>
   </si>
 </sst>
 </file>
@@ -701,6 +704,9 @@
       <c r="C7" t="s">
         <v>12</v>
       </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
       <c r="E7" t="s">
         <v>30</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC5E1B34-815B-F64D-957C-E29F55A82F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B9F33F-044C-0041-8052-E7CEF1ABE39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -202,6 +202,12 @@
   </si>
   <si>
     <t>/slides/06-Inference_for_Categorical_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/07-Inference_for_Numerical_Data.html</t>
+  </si>
+  <si>
+    <t>/slides/08-Linear_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -743,6 +749,9 @@
       <c r="C10" t="s">
         <v>13</v>
       </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
       <c r="E10" t="s">
         <v>32</v>
       </c>
@@ -760,6 +769,9 @@
       </c>
       <c r="C11" t="s">
         <v>14</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
       </c>
       <c r="E11" t="s">
         <v>33</v>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B9F33F-044C-0041-8052-E7CEF1ABE39D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D9515-CA83-5048-856F-5EB524310D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>/slides/08-Linear_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Logistic_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -791,6 +794,9 @@
       <c r="C12" t="s">
         <v>39</v>
       </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
       <c r="E12" t="s">
         <v>36</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863D9515-CA83-5048-856F-5EB524310D10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3004C767-9CAA-494D-B53B-F763E7C6E7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -789,7 +789,7 @@
         <v>45965</v>
       </c>
       <c r="B12" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>39</v>
@@ -798,10 +798,10 @@
         <v>58</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -810,16 +810,16 @@
         <v>45972</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -830,7 +830,6 @@
       <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="2"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3004C767-9CAA-494D-B53B-F763E7C6E7EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56239275-C0D2-1448-AD2E-96970229E1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>Date</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>/slides/09-Logistic_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Multiple_Regression.html</t>
   </si>
 </sst>
 </file>
@@ -815,6 +818,9 @@
       <c r="C13" t="s">
         <v>15</v>
       </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
       <c r="E13" t="s">
         <v>36</v>
       </c>

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56239275-C0D2-1448-AD2E-96970229E1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577D720-25E0-B94D-AC80-8FDEEE8BB238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>/slides/09-Multiple_Regression.html</t>
+  </si>
+  <si>
+    <t>/slides/09-Predictive_Modeling.html</t>
   </si>
 </sst>
 </file>
@@ -836,6 +839,9 @@
       <c r="B14" t="s">
         <v>22</v>
       </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="1">

--- a/Schedule.xlsx
+++ b/Schedule.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jasonbryer/Dropbox (Personal)/School/Teaching/DAV5300 2025 Fall/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9577D720-25E0-B94D-AC80-8FDEEE8BB238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F51F58A5-AA9E-4347-9195-EF1B62A41320}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2380" yWindow="4000" windowWidth="25340" windowHeight="14540" xr2:uid="{A772458D-4E7B-8249-8B6B-34FE7D5BD316}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
     <t>Date</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>/slides/09-Predictive_Modeling.html</t>
+  </si>
+  <si>
+    <t>/slides/10-Bayesian_and_PSA.html</t>
   </si>
 </sst>
 </file>
@@ -864,6 +867,9 @@
       <c r="C16" t="s">
         <v>16</v>
       </c>
+      <c r="D16" t="s">
+        <v>61</v>
+      </c>
       <c r="E16" s="2"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
